--- a/ksoft_old/docs/fields_details/Receipt_Detail.xlsx
+++ b/ksoft_old/docs/fields_details/Receipt_Detail.xlsx
@@ -1257,13 +1257,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{769EE35A-33A5-4FCC-9D17-C5DEF160CA07}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB4ECC3F-1464-45DA-BB5A-5925AA0F3990}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4E9EDD0-63CC-4670-9F13-8E956D612920}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{780B4D33-C86E-44D9-9AF6-D3E1DB2C2BD6}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{874F3512-B812-45EA-B832-0FA217B14BDD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C39A20A-E5E9-4C94-B00C-9ADB4AF900B8}"/>
 </file>
--- a/ksoft_old/docs/fields_details/Receipt_Detail.xlsx
+++ b/ksoft_old/docs/fields_details/Receipt_Detail.xlsx
@@ -1257,13 +1257,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB4ECC3F-1464-45DA-BB5A-5925AA0F3990}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C489A359-1A5A-4005-925B-BBA18CE4FD6C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{780B4D33-C86E-44D9-9AF6-D3E1DB2C2BD6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC14F456-592A-46FF-BB78-6D629B157BEE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C39A20A-E5E9-4C94-B00C-9ADB4AF900B8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{96F509BE-F4AA-4997-83F0-29BB7402C0CF}"/>
 </file>
--- a/ksoft_old/docs/fields_details/Receipt_Detail.xlsx
+++ b/ksoft_old/docs/fields_details/Receipt_Detail.xlsx
@@ -1257,13 +1257,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C489A359-1A5A-4005-925B-BBA18CE4FD6C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{769EE35A-33A5-4FCC-9D17-C5DEF160CA07}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC14F456-592A-46FF-BB78-6D629B157BEE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4E9EDD0-63CC-4670-9F13-8E956D612920}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{96F509BE-F4AA-4997-83F0-29BB7402C0CF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{874F3512-B812-45EA-B832-0FA217B14BDD}"/>
 </file>